--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="87">
   <si>
     <t>#</t>
   </si>
@@ -1307,7 +1307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2631,8 +2631,1009 @@
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
     </row>
+    <row r="19" customHeight="1" spans="3:28">
+      <c r="C19" s="1">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="1">
+        <v>400</v>
+      </c>
+      <c r="L19" s="1">
+        <v>250</v>
+      </c>
+      <c r="M19" s="1">
+        <f t="shared" ref="M19:M39" si="6">M18+5</f>
+        <v>5</v>
+      </c>
+      <c r="N19" s="1">
+        <f t="shared" ref="N19:N39" si="7">N18+10</f>
+        <v>10</v>
+      </c>
+      <c r="O19" s="1">
+        <v>78</v>
+      </c>
+      <c r="P19" s="1">
+        <v>80</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>13</v>
+      </c>
+      <c r="V19" s="5">
+        <v>13</v>
+      </c>
+      <c r="W19" s="1">
+        <v>90000</v>
+      </c>
+      <c r="X19" s="1">
+        <v>90000</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:28">
+      <c r="C20" s="1">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" ref="K20:K30" si="8">K19+150</f>
+        <v>550</v>
+      </c>
+      <c r="L20" s="1">
+        <f t="shared" ref="L20:L30" si="9">L19+70</f>
+        <v>320</v>
+      </c>
+      <c r="M20" s="1">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="N20" s="1">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="O20" s="1">
+        <f t="shared" ref="O20:O30" si="10">O19+6</f>
+        <v>84</v>
+      </c>
+      <c r="P20" s="1">
+        <f t="shared" ref="P20:P30" si="11">P19+6</f>
+        <v>86</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="1">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>14</v>
+      </c>
+      <c r="V20" s="5">
+        <v>14</v>
+      </c>
+      <c r="W20" s="1">
+        <v>100000</v>
+      </c>
+      <c r="X20" s="1">
+        <v>100000</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:28">
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K21" s="1">
+        <f t="shared" si="8"/>
+        <v>700</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="9"/>
+        <v>390</v>
+      </c>
+      <c r="M21" s="1">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="N21" s="1">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="O21" s="1">
+        <f t="shared" si="10"/>
+        <v>90</v>
+      </c>
+      <c r="P21" s="1">
+        <f t="shared" si="11"/>
+        <v>92</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
+        <v>15</v>
+      </c>
+      <c r="V21" s="5">
+        <v>15</v>
+      </c>
+      <c r="W21" s="1">
+        <v>120000</v>
+      </c>
+      <c r="X21" s="1">
+        <v>120000</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z21" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:28">
+      <c r="C22" s="1">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K22" s="1">
+        <f t="shared" si="8"/>
+        <v>850</v>
+      </c>
+      <c r="L22" s="1">
+        <f t="shared" si="9"/>
+        <v>460</v>
+      </c>
+      <c r="M22" s="1">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="N22" s="1">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="O22" s="1">
+        <f t="shared" si="10"/>
+        <v>96</v>
+      </c>
+      <c r="P22" s="1">
+        <f t="shared" si="11"/>
+        <v>98</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>16</v>
+      </c>
+      <c r="V22" s="5">
+        <v>16</v>
+      </c>
+      <c r="W22" s="1">
+        <v>140000</v>
+      </c>
+      <c r="X22" s="1">
+        <v>140000</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z22" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:28">
+      <c r="C23" s="1">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="1">
+        <v>5</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23" s="1">
+        <f t="shared" si="8"/>
+        <v>1000</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="9"/>
+        <v>530</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="N23" s="1">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="O23" s="1">
+        <f t="shared" si="10"/>
+        <v>102</v>
+      </c>
+      <c r="P23" s="1">
+        <f t="shared" si="11"/>
+        <v>104</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <v>17</v>
+      </c>
+      <c r="V23" s="5">
+        <v>17</v>
+      </c>
+      <c r="W23" s="1">
+        <v>160000</v>
+      </c>
+      <c r="X23" s="1">
+        <v>160000</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z23" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
     <row r="24" customHeight="1" spans="3:28">
-      <c r="J24" s="1"/>
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="1">
+        <v>6</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K24" s="1">
+        <f t="shared" si="8"/>
+        <v>1150</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" si="9"/>
+        <v>600</v>
+      </c>
+      <c r="M24" s="1">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="N24" s="1">
+        <f t="shared" si="7"/>
+        <v>60</v>
+      </c>
+      <c r="O24" s="1">
+        <f t="shared" si="10"/>
+        <v>108</v>
+      </c>
+      <c r="P24" s="1">
+        <f t="shared" si="11"/>
+        <v>110</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5">
+        <v>18</v>
+      </c>
+      <c r="V24" s="5">
+        <v>18</v>
+      </c>
+      <c r="W24" s="1">
+        <v>180000</v>
+      </c>
+      <c r="X24" s="1">
+        <v>180000</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z24" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:28">
+      <c r="C25" s="1">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="1">
+        <v>7</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K25" s="1">
+        <f t="shared" si="8"/>
+        <v>1300</v>
+      </c>
+      <c r="L25" s="1">
+        <f t="shared" si="9"/>
+        <v>670</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+      <c r="N25" s="1">
+        <f t="shared" si="7"/>
+        <v>70</v>
+      </c>
+      <c r="O25" s="1">
+        <f t="shared" si="10"/>
+        <v>114</v>
+      </c>
+      <c r="P25" s="1">
+        <f t="shared" si="11"/>
+        <v>116</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>0</v>
+      </c>
+      <c r="T25" s="1">
+        <v>0</v>
+      </c>
+      <c r="U25" s="5">
+        <v>19</v>
+      </c>
+      <c r="V25" s="5">
+        <v>19</v>
+      </c>
+      <c r="W25" s="1">
+        <v>200000</v>
+      </c>
+      <c r="X25" s="1">
+        <v>200000</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:28">
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="1">
+        <v>8</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="1">
+        <f t="shared" si="8"/>
+        <v>1450</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="9"/>
+        <v>740</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="6"/>
+        <v>40</v>
+      </c>
+      <c r="N26" s="1">
+        <f t="shared" si="7"/>
+        <v>80</v>
+      </c>
+      <c r="O26" s="1">
+        <f t="shared" si="10"/>
+        <v>120</v>
+      </c>
+      <c r="P26" s="1">
+        <f t="shared" si="11"/>
+        <v>122</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1">
+        <v>0</v>
+      </c>
+      <c r="T26" s="1">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5">
+        <v>20</v>
+      </c>
+      <c r="V26" s="5">
+        <v>20</v>
+      </c>
+      <c r="W26" s="1">
+        <v>220000</v>
+      </c>
+      <c r="X26" s="1">
+        <v>220000</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z26" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:28">
+      <c r="C27" s="1">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="1">
+        <v>9</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K27" s="1">
+        <f t="shared" si="8"/>
+        <v>1600</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="9"/>
+        <v>810</v>
+      </c>
+      <c r="M27" s="1">
+        <f t="shared" si="6"/>
+        <v>45</v>
+      </c>
+      <c r="N27" s="1">
+        <f t="shared" si="7"/>
+        <v>90</v>
+      </c>
+      <c r="O27" s="1">
+        <f t="shared" si="10"/>
+        <v>126</v>
+      </c>
+      <c r="P27" s="1">
+        <f t="shared" si="11"/>
+        <v>128</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
+      <c r="U27" s="5">
+        <v>21</v>
+      </c>
+      <c r="V27" s="5">
+        <v>21</v>
+      </c>
+      <c r="W27" s="1">
+        <v>240000</v>
+      </c>
+      <c r="X27" s="1">
+        <v>240000</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z27" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:28">
+      <c r="C28" s="1">
+        <v>22</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K28" s="1">
+        <f t="shared" si="8"/>
+        <v>1750</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="9"/>
+        <v>880</v>
+      </c>
+      <c r="M28" s="1">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="N28" s="1">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+      <c r="O28" s="1">
+        <f t="shared" si="10"/>
+        <v>132</v>
+      </c>
+      <c r="P28" s="1">
+        <f t="shared" si="11"/>
+        <v>134</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+      <c r="S28" s="1">
+        <v>0</v>
+      </c>
+      <c r="T28" s="1">
+        <v>0</v>
+      </c>
+      <c r="U28" s="5">
+        <v>22</v>
+      </c>
+      <c r="V28" s="5">
+        <v>22</v>
+      </c>
+      <c r="W28" s="1">
+        <v>260000</v>
+      </c>
+      <c r="X28" s="1">
+        <v>260000</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z28" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:28">
+      <c r="C29" s="1">
+        <v>23</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="1">
+        <v>11</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K29" s="1">
+        <f t="shared" si="8"/>
+        <v>1900</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="9"/>
+        <v>950</v>
+      </c>
+      <c r="M29" s="1">
+        <f t="shared" si="6"/>
+        <v>55</v>
+      </c>
+      <c r="N29" s="1">
+        <f t="shared" si="7"/>
+        <v>110</v>
+      </c>
+      <c r="O29" s="1">
+        <f t="shared" si="10"/>
+        <v>138</v>
+      </c>
+      <c r="P29" s="1">
+        <f t="shared" si="11"/>
+        <v>140</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+      <c r="S29" s="1">
+        <v>0</v>
+      </c>
+      <c r="T29" s="1">
+        <v>0</v>
+      </c>
+      <c r="U29" s="5">
+        <v>23</v>
+      </c>
+      <c r="V29" s="5">
+        <v>23</v>
+      </c>
+      <c r="W29" s="1">
+        <v>280000</v>
+      </c>
+      <c r="X29" s="1">
+        <v>280000</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:28">
+      <c r="C30" s="1">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="1">
+        <v>12</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K30" s="1">
+        <f t="shared" si="8"/>
+        <v>2050</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="9"/>
+        <v>1020</v>
+      </c>
+      <c r="M30" s="1">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="N30" s="1">
+        <f t="shared" si="7"/>
+        <v>120</v>
+      </c>
+      <c r="O30" s="1">
+        <f t="shared" si="10"/>
+        <v>144</v>
+      </c>
+      <c r="P30" s="1">
+        <f t="shared" si="11"/>
+        <v>146</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30" s="1">
+        <v>0</v>
+      </c>
+      <c r="T30" s="1">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5">
+        <v>24</v>
+      </c>
+      <c r="V30" s="5">
+        <v>24</v>
+      </c>
+      <c r="W30" s="1">
+        <v>300000</v>
+      </c>
+      <c r="X30" s="1">
+        <v>300000</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>18000</v>
+      </c>
+      <c r="Z30" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="123">
   <si>
     <t>#</t>
   </si>
@@ -325,6 +325,114 @@
   </si>
   <si>
     <t>1002,1003,1004</t>
+  </si>
+  <si>
+    <t>178E+7</t>
+  </si>
+  <si>
+    <t>797E+7</t>
+  </si>
+  <si>
+    <t>167E+13</t>
+  </si>
+  <si>
+    <t>388E+7</t>
+  </si>
+  <si>
+    <t>255E+8</t>
+  </si>
+  <si>
+    <t>632E+13</t>
+  </si>
+  <si>
+    <t>788E+7</t>
+  </si>
+  <si>
+    <t>810E+8</t>
+  </si>
+  <si>
+    <t>238E+14</t>
+  </si>
+  <si>
+    <t>171E+8</t>
+  </si>
+  <si>
+    <t>255E+9</t>
+  </si>
+  <si>
+    <t>900E+14</t>
+  </si>
+  <si>
+    <t>384E+8</t>
+  </si>
+  <si>
+    <t>806E+9</t>
+  </si>
+  <si>
+    <t>338E+15</t>
+  </si>
+  <si>
+    <t>832E+8</t>
+  </si>
+  <si>
+    <t>252E+10</t>
+  </si>
+  <si>
+    <t>127E+16</t>
+  </si>
+  <si>
+    <t>183E+9</t>
+  </si>
+  <si>
+    <t>791E+10</t>
+  </si>
+  <si>
+    <t>477E+16</t>
+  </si>
+  <si>
+    <t>399E+9</t>
+  </si>
+  <si>
+    <t>246E+11</t>
+  </si>
+  <si>
+    <t>178E+17</t>
+  </si>
+  <si>
+    <t>877E+9</t>
+  </si>
+  <si>
+    <t>763E+11</t>
+  </si>
+  <si>
+    <t>662E+17</t>
+  </si>
+  <si>
+    <t>192E+10</t>
+  </si>
+  <si>
+    <t>238E+12</t>
+  </si>
+  <si>
+    <t>245E+18</t>
+  </si>
+  <si>
+    <t>421E+10</t>
+  </si>
+  <si>
+    <t>736E+12</t>
+  </si>
+  <si>
+    <t>915E+18</t>
+  </si>
+  <si>
+    <t>920E+10</t>
+  </si>
+  <si>
+    <t>229E+13</t>
+  </si>
+  <si>
+    <t>341E+19</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1433,7 @@
     <col min="14" max="14" width="10.25" style="2" customWidth="1"/>
     <col min="15" max="15" width="8.08333333333333" style="2" customWidth="1"/>
     <col min="16" max="16" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.16666666666667" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.5833333333333" style="2" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="2" customWidth="1"/>
     <col min="19" max="20" width="8.75" style="2" customWidth="1"/>
     <col min="21" max="21" width="7.50833333333333" style="2" customWidth="1"/>
@@ -2648,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K19" s="1">
         <v>400</v>
@@ -2663,12 +2771,10 @@
         <v>250</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" ref="M19:M39" si="6">M18+5</f>
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="N19" s="1">
-        <f t="shared" ref="N19:N39" si="7">N18+10</f>
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="O19" s="1">
         <v>78</v>
@@ -2677,7 +2783,7 @@
         <v>80</v>
       </c>
       <c r="Q19" s="1">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R19" s="1">
         <v>0</v>
@@ -2728,29 +2834,29 @@
         <v>2</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K20" s="1">
-        <f t="shared" ref="K20:K30" si="8">K19+150</f>
+        <f t="shared" ref="K20:K30" si="6">K19+150</f>
         <v>550</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" ref="L20:L30" si="9">L19+70</f>
+        <f t="shared" ref="L20:L30" si="7">L19+70</f>
         <v>320</v>
       </c>
       <c r="M20" s="1">
-        <f t="shared" si="6"/>
-        <v>10</v>
+        <f t="shared" ref="M19:M39" si="8">M19+5</f>
+        <v>80</v>
       </c>
       <c r="N20" s="1">
-        <f t="shared" si="7"/>
-        <v>20</v>
+        <f t="shared" ref="N20:N30" si="9">N19+100</f>
+        <v>400</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" ref="O20:O30" si="10">O19+6</f>
@@ -2761,7 +2867,7 @@
         <v>86</v>
       </c>
       <c r="Q20" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -2812,29 +2918,29 @@
         <v>3</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J21" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K21" s="1">
+        <f t="shared" si="6"/>
+        <v>700</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="7"/>
+        <v>390</v>
+      </c>
+      <c r="M21" s="1">
+        <f t="shared" si="8"/>
         <v>85</v>
       </c>
-      <c r="K21" s="1">
-        <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="L21" s="1">
+      <c r="N21" s="1">
         <f t="shared" si="9"/>
-        <v>390</v>
-      </c>
-      <c r="M21" s="1">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="N21" s="1">
-        <f t="shared" si="7"/>
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" si="10"/>
@@ -2845,7 +2951,7 @@
         <v>92</v>
       </c>
       <c r="Q21" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R21" s="1">
         <v>0</v>
@@ -2896,29 +3002,29 @@
         <v>4</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="K22" s="1">
+        <f t="shared" si="6"/>
+        <v>850</v>
+      </c>
+      <c r="L22" s="1">
+        <f t="shared" si="7"/>
+        <v>460</v>
+      </c>
+      <c r="M22" s="1">
         <f t="shared" si="8"/>
-        <v>850</v>
-      </c>
-      <c r="L22" s="1">
+        <v>90</v>
+      </c>
+      <c r="N22" s="1">
         <f t="shared" si="9"/>
-        <v>460</v>
-      </c>
-      <c r="M22" s="1">
-        <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="N22" s="1">
-        <f t="shared" si="7"/>
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="O22" s="1">
         <f t="shared" si="10"/>
@@ -2929,7 +3035,7 @@
         <v>98</v>
       </c>
       <c r="Q22" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R22" s="1">
         <v>0</v>
@@ -2980,29 +3086,29 @@
         <v>5</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K23" s="1">
+        <f t="shared" si="6"/>
+        <v>1000</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="7"/>
+        <v>530</v>
+      </c>
+      <c r="M23" s="1">
         <f t="shared" si="8"/>
-        <v>1000</v>
-      </c>
-      <c r="L23" s="1">
+        <v>95</v>
+      </c>
+      <c r="N23" s="1">
         <f t="shared" si="9"/>
-        <v>530</v>
-      </c>
-      <c r="M23" s="1">
-        <f t="shared" si="6"/>
-        <v>25</v>
-      </c>
-      <c r="N23" s="1">
-        <f t="shared" si="7"/>
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" si="10"/>
@@ -3013,7 +3119,7 @@
         <v>104</v>
       </c>
       <c r="Q23" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R23" s="1">
         <v>0</v>
@@ -3064,29 +3170,29 @@
         <v>6</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="K24" s="1">
+        <f t="shared" si="6"/>
+        <v>1150</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" si="7"/>
+        <v>600</v>
+      </c>
+      <c r="M24" s="1">
         <f t="shared" si="8"/>
-        <v>1150</v>
-      </c>
-      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+      <c r="N24" s="1">
         <f t="shared" si="9"/>
-        <v>600</v>
-      </c>
-      <c r="M24" s="1">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="N24" s="1">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" si="10"/>
@@ -3097,7 +3203,7 @@
         <v>110</v>
       </c>
       <c r="Q24" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R24" s="1">
         <v>0</v>
@@ -3148,29 +3254,29 @@
         <v>7</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="K25" s="1">
+        <f t="shared" si="6"/>
+        <v>1300</v>
+      </c>
+      <c r="L25" s="1">
+        <f t="shared" si="7"/>
+        <v>670</v>
+      </c>
+      <c r="M25" s="1">
         <f t="shared" si="8"/>
-        <v>1300</v>
-      </c>
-      <c r="L25" s="1">
+        <v>105</v>
+      </c>
+      <c r="N25" s="1">
         <f t="shared" si="9"/>
-        <v>670</v>
-      </c>
-      <c r="M25" s="1">
-        <f t="shared" si="6"/>
-        <v>35</v>
-      </c>
-      <c r="N25" s="1">
-        <f t="shared" si="7"/>
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" si="10"/>
@@ -3181,7 +3287,7 @@
         <v>116</v>
       </c>
       <c r="Q25" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R25" s="1">
         <v>0</v>
@@ -3232,29 +3338,29 @@
         <v>8</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="K26" s="1">
+        <f t="shared" si="6"/>
+        <v>1450</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="7"/>
+        <v>740</v>
+      </c>
+      <c r="M26" s="1">
         <f t="shared" si="8"/>
-        <v>1450</v>
-      </c>
-      <c r="L26" s="1">
+        <v>110</v>
+      </c>
+      <c r="N26" s="1">
         <f t="shared" si="9"/>
-        <v>740</v>
-      </c>
-      <c r="M26" s="1">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="N26" s="1">
-        <f t="shared" si="7"/>
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" si="10"/>
@@ -3265,7 +3371,7 @@
         <v>122</v>
       </c>
       <c r="Q26" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R26" s="1">
         <v>0</v>
@@ -3316,29 +3422,29 @@
         <v>9</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="K27" s="1">
+        <f t="shared" si="6"/>
+        <v>1600</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="7"/>
+        <v>810</v>
+      </c>
+      <c r="M27" s="1">
         <f t="shared" si="8"/>
-        <v>1600</v>
-      </c>
-      <c r="L27" s="1">
+        <v>115</v>
+      </c>
+      <c r="N27" s="1">
         <f t="shared" si="9"/>
-        <v>810</v>
-      </c>
-      <c r="M27" s="1">
-        <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-      <c r="N27" s="1">
-        <f t="shared" si="7"/>
-        <v>90</v>
+        <v>1100</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="10"/>
@@ -3349,7 +3455,7 @@
         <v>128</v>
       </c>
       <c r="Q27" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R27" s="1">
         <v>0</v>
@@ -3400,29 +3506,29 @@
         <v>10</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="K28" s="1">
+        <f t="shared" si="6"/>
+        <v>1750</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="7"/>
+        <v>880</v>
+      </c>
+      <c r="M28" s="1">
         <f t="shared" si="8"/>
-        <v>1750</v>
-      </c>
-      <c r="L28" s="1">
+        <v>120</v>
+      </c>
+      <c r="N28" s="1">
         <f t="shared" si="9"/>
-        <v>880</v>
-      </c>
-      <c r="M28" s="1">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-      <c r="N28" s="1">
-        <f t="shared" si="7"/>
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" si="10"/>
@@ -3433,7 +3539,7 @@
         <v>134</v>
       </c>
       <c r="Q28" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R28" s="1">
         <v>0</v>
@@ -3484,29 +3590,29 @@
         <v>11</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="K29" s="1">
+        <f t="shared" si="6"/>
+        <v>1900</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="7"/>
+        <v>950</v>
+      </c>
+      <c r="M29" s="1">
         <f t="shared" si="8"/>
-        <v>1900</v>
-      </c>
-      <c r="L29" s="1">
+        <v>125</v>
+      </c>
+      <c r="N29" s="1">
         <f t="shared" si="9"/>
-        <v>950</v>
-      </c>
-      <c r="M29" s="1">
-        <f t="shared" si="6"/>
-        <v>55</v>
-      </c>
-      <c r="N29" s="1">
-        <f t="shared" si="7"/>
-        <v>110</v>
+        <v>1300</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" si="10"/>
@@ -3517,7 +3623,7 @@
         <v>140</v>
       </c>
       <c r="Q29" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R29" s="1">
         <v>0</v>
@@ -3568,29 +3674,29 @@
         <v>12</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="K30" s="1">
+        <f t="shared" si="6"/>
+        <v>2050</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="7"/>
+        <v>1020</v>
+      </c>
+      <c r="M30" s="1">
         <f t="shared" si="8"/>
-        <v>2050</v>
-      </c>
-      <c r="L30" s="1">
+        <v>130</v>
+      </c>
+      <c r="N30" s="1">
         <f t="shared" si="9"/>
-        <v>1020</v>
-      </c>
-      <c r="M30" s="1">
-        <f t="shared" si="6"/>
-        <v>60</v>
-      </c>
-      <c r="N30" s="1">
-        <f t="shared" si="7"/>
-        <v>120</v>
+        <v>1400</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" si="10"/>
@@ -3601,7 +3707,7 @@
         <v>146</v>
       </c>
       <c r="Q30" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R30" s="1">
         <v>0</v>
@@ -3637,7 +3743,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5 Z3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:V5 Z3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -612,12 +612,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3743,7 +3743,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:V5 Z3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5 Z3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -348,7 +348,7 @@
     <t>788E+7</t>
   </si>
   <si>
-    <t>810E+8</t>
+    <t>891E+8</t>
   </si>
   <si>
     <t>238E+14</t>
@@ -357,7 +357,7 @@
     <t>171E+8</t>
   </si>
   <si>
-    <t>255E+9</t>
+    <t>432E+9</t>
   </si>
   <si>
     <t>900E+14</t>
@@ -366,7 +366,7 @@
     <t>384E+8</t>
   </si>
   <si>
-    <t>806E+9</t>
+    <t>185E+10</t>
   </si>
   <si>
     <t>338E+15</t>
@@ -375,7 +375,7 @@
     <t>832E+8</t>
   </si>
   <si>
-    <t>252E+10</t>
+    <t>731E+10</t>
   </si>
   <si>
     <t>127E+16</t>
@@ -384,7 +384,7 @@
     <t>183E+9</t>
   </si>
   <si>
-    <t>791E+10</t>
+    <t>277E+11</t>
   </si>
   <si>
     <t>477E+16</t>
@@ -393,7 +393,7 @@
     <t>399E+9</t>
   </si>
   <si>
-    <t>246E+11</t>
+    <t>100E+12</t>
   </si>
   <si>
     <t>178E+17</t>
@@ -402,7 +402,7 @@
     <t>877E+9</t>
   </si>
   <si>
-    <t>763E+11</t>
+    <t>357E+12</t>
   </si>
   <si>
     <t>662E+17</t>
@@ -411,7 +411,7 @@
     <t>192E+10</t>
   </si>
   <si>
-    <t>238E+12</t>
+    <t>125E+13</t>
   </si>
   <si>
     <t>245E+18</t>
@@ -420,7 +420,7 @@
     <t>421E+10</t>
   </si>
   <si>
-    <t>736E+12</t>
+    <t>435E+13</t>
   </si>
   <si>
     <t>915E+18</t>
@@ -429,7 +429,7 @@
     <t>920E+10</t>
   </si>
   <si>
-    <t>229E+13</t>
+    <t>149E+14</t>
   </si>
   <si>
     <t>341E+19</t>
@@ -612,12 +612,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3743,7 +3743,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:V5 Z3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5 J3:V5 Z3:AA5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/BossConfig.xlsx
+++ b/Excel/BossConfig.xlsx
@@ -37,7 +37,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="Y3" authorId="0">
+    <comment ref="Z3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="124">
   <si>
     <t>#</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>CritDamage</t>
+  </si>
+  <si>
+    <t>MulDamageResit</t>
   </si>
   <si>
     <t>Accuracy</t>
@@ -1415,7 +1418,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1430,22 +1433,22 @@
     <col min="10" max="11" width="11" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.1666666666667" style="2" customWidth="1"/>
     <col min="13" max="13" width="10" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.25" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8.08333333333333" style="2" customWidth="1"/>
-    <col min="16" max="16" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.5833333333333" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.5" style="2" customWidth="1"/>
-    <col min="19" max="20" width="8.75" style="2" customWidth="1"/>
-    <col min="21" max="21" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="22" max="22" width="8.33333333333333" style="2" customWidth="1"/>
-    <col min="23" max="23" width="11.6666666666667" style="2" customWidth="1"/>
-    <col min="24" max="24" width="11.1666666666667" style="2" customWidth="1"/>
-    <col min="25" max="27" width="14.25" style="2" customWidth="1"/>
-    <col min="28" max="28" width="11.8333333333333" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="2"/>
+    <col min="14" max="15" width="10.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8.08333333333333" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.91666666666667" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11.5833333333333" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.5" style="2" customWidth="1"/>
+    <col min="20" max="21" width="8.75" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="23" max="23" width="8.33333333333333" style="2" customWidth="1"/>
+    <col min="24" max="24" width="11.6666666666667" style="2" customWidth="1"/>
+    <col min="25" max="25" width="11.1666666666667" style="2" customWidth="1"/>
+    <col min="26" max="28" width="14.25" style="2" customWidth="1"/>
+    <col min="29" max="29" width="11.8333333333333" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="3"/>
@@ -1468,11 +1471,12 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="I2" s="2"/>
@@ -1494,11 +1498,12 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1576,33 +1581,36 @@
       <c r="AA3" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="AB3" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>9</v>
@@ -1641,13 +1649,13 @@
         <v>20</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="X4" s="4" t="s">
         <v>33</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Z4" s="4" t="s">
         <v>24</v>
@@ -1655,90 +1663,96 @@
       <c r="AA4" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="AB4" s="4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="H5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="N5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB5" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="AB5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1749,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1761,7 +1775,7 @@
         <v>10000</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6" s="1">
         <v>50</v>
@@ -1775,15 +1789,12 @@
       <c r="N6" s="1">
         <v>30</v>
       </c>
-      <c r="O6" s="5">
+      <c r="P6" s="5">
         <v>10</v>
       </c>
-      <c r="P6" s="5">
+      <c r="Q6" s="5">
         <v>20</v>
       </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
       <c r="R6" s="1">
         <v>0</v>
       </c>
@@ -1793,26 +1804,29 @@
       <c r="T6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="5">
-        <v>1</v>
+      <c r="U6" s="1">
+        <v>0</v>
       </c>
       <c r="V6" s="5">
         <v>1</v>
       </c>
-      <c r="W6" s="1">
-        <v>5000</v>
+      <c r="W6" s="5">
+        <v>1</v>
       </c>
       <c r="X6" s="1">
         <v>5000</v>
       </c>
       <c r="Y6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="Z6" s="1">
         <v>4500</v>
       </c>
-      <c r="AB6" s="1" t="s">
-        <v>41</v>
+      <c r="AC6" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" customHeight="1" spans="1:29">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1823,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -1835,7 +1849,7 @@
         <v>100000</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" ref="K7:K17" si="0">K6+25</f>
@@ -1853,17 +1867,15 @@
         <f t="shared" ref="N7:N17" si="3">N6+10</f>
         <v>40</v>
       </c>
-      <c r="O7" s="1">
-        <f t="shared" ref="O7:O17" si="4">O6+5</f>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <f t="shared" ref="P7:P17" si="4">P6+5</f>
         <v>15</v>
       </c>
-      <c r="P7" s="1">
-        <f t="shared" ref="P7:P17" si="5">P6+5</f>
+      <c r="Q7" s="1">
+        <f t="shared" ref="Q7:Q17" si="5">Q6+5</f>
         <v>25</v>
       </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
       <c r="R7" s="1">
         <v>0</v>
       </c>
@@ -1873,28 +1885,31 @@
       <c r="T7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="5">
-        <v>2</v>
+      <c r="U7" s="1">
+        <v>0</v>
       </c>
       <c r="V7" s="5">
         <v>2</v>
       </c>
-      <c r="W7" s="1">
-        <v>8000</v>
+      <c r="W7" s="5">
+        <v>2</v>
       </c>
       <c r="X7" s="1">
         <v>8000</v>
       </c>
       <c r="Y7" s="1">
+        <v>8000</v>
+      </c>
+      <c r="Z7" s="1">
         <v>6000</v>
       </c>
-      <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
-      <c r="AB7" s="2" t="s">
-        <v>44</v>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:28">
+    <row r="8" customHeight="1" spans="1:29">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1905,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
@@ -1917,7 +1932,7 @@
         <v>400000</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
@@ -1935,17 +1950,15 @@
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="O8" s="1">
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="P8" s="1">
+      <c r="Q8" s="1">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
       <c r="R8" s="1">
         <v>0</v>
       </c>
@@ -1955,28 +1968,31 @@
       <c r="T8" s="1">
         <v>0</v>
       </c>
-      <c r="U8" s="5">
-        <v>3</v>
+      <c r="U8" s="1">
+        <v>0</v>
       </c>
       <c r="V8" s="5">
         <v>3</v>
       </c>
-      <c r="W8" s="1">
-        <v>10000</v>
+      <c r="W8" s="5">
+        <v>3</v>
       </c>
       <c r="X8" s="1">
         <v>10000</v>
       </c>
       <c r="Y8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Z8" s="1">
         <v>8000</v>
       </c>
-      <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
-      <c r="AB8" s="2" t="s">
-        <v>47</v>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:28">
+    <row r="9" customHeight="1" spans="1:29">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1987,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
@@ -1999,7 +2015,7 @@
         <v>2000000</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
@@ -2017,17 +2033,15 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="O9" s="1">
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
       <c r="R9" s="1">
         <v>0</v>
       </c>
@@ -2037,30 +2051,33 @@
       <c r="T9" s="1">
         <v>0</v>
       </c>
-      <c r="U9" s="5">
-        <v>4</v>
+      <c r="U9" s="1">
+        <v>0</v>
       </c>
       <c r="V9" s="5">
         <v>4</v>
       </c>
-      <c r="W9" s="1">
-        <v>15000</v>
+      <c r="W9" s="5">
+        <v>4</v>
       </c>
       <c r="X9" s="1">
         <v>15000</v>
       </c>
       <c r="Y9" s="1">
+        <v>15000</v>
+      </c>
+      <c r="Z9" s="1">
         <v>10000</v>
       </c>
-      <c r="Z9" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="2" t="s">
+      <c r="AA9" s="7" t="s">
         <v>51</v>
       </c>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="10" customHeight="1" spans="1:28">
+    <row r="10" customHeight="1" spans="1:29">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -2071,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -2080,10 +2097,10 @@
         <v>1000000</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="0"/>
@@ -2101,17 +2118,15 @@
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
       <c r="R10" s="1">
         <v>0</v>
       </c>
@@ -2121,30 +2136,33 @@
       <c r="T10" s="1">
         <v>0</v>
       </c>
-      <c r="U10" s="5">
-        <v>5</v>
+      <c r="U10" s="1">
+        <v>0</v>
       </c>
       <c r="V10" s="5">
         <v>5</v>
       </c>
-      <c r="W10" s="1">
-        <v>20000</v>
+      <c r="W10" s="5">
+        <v>5</v>
       </c>
       <c r="X10" s="1">
         <v>20000</v>
       </c>
       <c r="Y10" s="1">
+        <v>20000</v>
+      </c>
+      <c r="Z10" s="1">
         <v>12000</v>
       </c>
-      <c r="Z10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="2" t="s">
+      <c r="AA10" s="7" t="s">
         <v>55</v>
       </c>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="11" customHeight="1" spans="1:28">
+    <row r="11" customHeight="1" spans="1:29">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -2155,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
@@ -2164,10 +2182,10 @@
         <v>3000000</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" si="0"/>
@@ -2185,17 +2203,15 @@
         <f t="shared" si="3"/>
         <v>80</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
       <c r="R11" s="1">
         <v>0</v>
       </c>
@@ -2205,30 +2221,33 @@
       <c r="T11" s="1">
         <v>0</v>
       </c>
-      <c r="U11" s="5">
-        <v>6</v>
+      <c r="U11" s="1">
+        <v>0</v>
       </c>
       <c r="V11" s="5">
         <v>6</v>
       </c>
-      <c r="W11" s="1">
-        <v>25000</v>
+      <c r="W11" s="5">
+        <v>6</v>
       </c>
       <c r="X11" s="1">
         <v>25000</v>
       </c>
       <c r="Y11" s="1">
+        <v>25000</v>
+      </c>
+      <c r="Z11" s="1">
         <v>14000</v>
       </c>
-      <c r="Z11" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="2" t="s">
-        <v>55</v>
+      <c r="AA11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:28">
+    <row r="12" customHeight="1" spans="1:29">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2239,19 +2258,19 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="0"/>
@@ -2269,17 +2288,15 @@
         <f t="shared" si="3"/>
         <v>90</v>
       </c>
-      <c r="O12" s="1">
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
       <c r="R12" s="1">
         <v>0</v>
       </c>
@@ -2289,30 +2306,33 @@
       <c r="T12" s="1">
         <v>0</v>
       </c>
-      <c r="U12" s="5">
-        <v>7</v>
+      <c r="U12" s="1">
+        <v>0</v>
       </c>
       <c r="V12" s="5">
         <v>7</v>
       </c>
-      <c r="W12" s="1">
-        <v>30000</v>
+      <c r="W12" s="5">
+        <v>7</v>
       </c>
       <c r="X12" s="1">
         <v>30000</v>
       </c>
       <c r="Y12" s="1">
+        <v>30000</v>
+      </c>
+      <c r="Z12" s="1">
         <v>16000</v>
       </c>
-      <c r="Z12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="2" t="s">
-        <v>55</v>
+      <c r="AA12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:28">
+    <row r="13" customHeight="1" spans="1:29">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2323,19 +2343,19 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="0"/>
@@ -2353,17 +2373,15 @@
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="O13" s="1">
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="P13" s="1">
+      <c r="Q13" s="1">
         <f t="shared" si="5"/>
         <v>55</v>
       </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
       <c r="R13" s="1">
         <v>0</v>
       </c>
@@ -2373,30 +2391,33 @@
       <c r="T13" s="1">
         <v>0</v>
       </c>
-      <c r="U13" s="5">
-        <v>8</v>
+      <c r="U13" s="1">
+        <v>0</v>
       </c>
       <c r="V13" s="5">
         <v>8</v>
       </c>
-      <c r="W13" s="1">
-        <v>40000</v>
+      <c r="W13" s="5">
+        <v>8</v>
       </c>
       <c r="X13" s="1">
         <v>40000</v>
       </c>
       <c r="Y13" s="1">
+        <v>40000</v>
+      </c>
+      <c r="Z13" s="1">
         <v>18000</v>
       </c>
-      <c r="Z13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="2" t="s">
-        <v>55</v>
+      <c r="AA13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" customHeight="1" spans="1:29">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2407,19 +2428,19 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="0"/>
@@ -2437,17 +2458,15 @@
         <f t="shared" si="3"/>
         <v>110</v>
       </c>
-      <c r="O14" s="1">
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="P14" s="1">
+      <c r="Q14" s="1">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
       <c r="R14" s="1">
         <v>0</v>
       </c>
@@ -2457,30 +2476,33 @@
       <c r="T14" s="1">
         <v>0</v>
       </c>
-      <c r="U14" s="5">
-        <v>9</v>
+      <c r="U14" s="1">
+        <v>0</v>
       </c>
       <c r="V14" s="5">
         <v>9</v>
       </c>
-      <c r="W14" s="1">
-        <v>50000</v>
+      <c r="W14" s="5">
+        <v>9</v>
       </c>
       <c r="X14" s="1">
         <v>50000</v>
       </c>
       <c r="Y14" s="1">
+        <v>50000</v>
+      </c>
+      <c r="Z14" s="1">
         <v>18000</v>
       </c>
-      <c r="Z14" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="2" t="s">
-        <v>55</v>
+      <c r="AA14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" customHeight="1" spans="1:29">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2491,19 +2513,19 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="0"/>
@@ -2521,17 +2543,15 @@
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="O15" s="1">
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="P15" s="1">
+      <c r="Q15" s="1">
         <f t="shared" si="5"/>
         <v>65</v>
       </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
       <c r="R15" s="1">
         <v>0</v>
       </c>
@@ -2541,30 +2561,33 @@
       <c r="T15" s="1">
         <v>0</v>
       </c>
-      <c r="U15" s="5">
-        <v>10</v>
+      <c r="U15" s="1">
+        <v>0</v>
       </c>
       <c r="V15" s="5">
         <v>10</v>
       </c>
-      <c r="W15" s="1">
-        <v>60000</v>
+      <c r="W15" s="5">
+        <v>10</v>
       </c>
       <c r="X15" s="1">
         <v>60000</v>
       </c>
       <c r="Y15" s="1">
+        <v>60000</v>
+      </c>
+      <c r="Z15" s="1">
         <v>18000</v>
       </c>
-      <c r="Z15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="2" t="s">
-        <v>55</v>
+      <c r="AA15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:28">
+    <row r="16" customHeight="1" spans="1:29">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2575,19 +2598,19 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="0"/>
@@ -2605,17 +2628,15 @@
         <f t="shared" si="3"/>
         <v>130</v>
       </c>
-      <c r="O16" s="1">
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="P16" s="1">
+      <c r="Q16" s="1">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
       <c r="R16" s="1">
         <v>0</v>
       </c>
@@ -2625,30 +2646,33 @@
       <c r="T16" s="1">
         <v>0</v>
       </c>
-      <c r="U16" s="5">
-        <v>11</v>
+      <c r="U16" s="1">
+        <v>0</v>
       </c>
       <c r="V16" s="5">
         <v>11</v>
       </c>
-      <c r="W16" s="1">
-        <v>70000</v>
+      <c r="W16" s="5">
+        <v>11</v>
       </c>
       <c r="X16" s="1">
         <v>70000</v>
       </c>
       <c r="Y16" s="1">
+        <v>70000</v>
+      </c>
+      <c r="Z16" s="1">
         <v>18000</v>
       </c>
-      <c r="Z16" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="2" t="s">
-        <v>55</v>
+      <c r="AA16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:28">
+    <row r="17" customHeight="1" spans="3:29">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2659,19 +2683,19 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="0"/>
@@ -2689,17 +2713,15 @@
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
         <f t="shared" si="4"/>
         <v>65</v>
       </c>
-      <c r="P17" s="1">
+      <c r="Q17" s="1">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
       <c r="R17" s="1">
         <v>0</v>
       </c>
@@ -2709,37 +2731,40 @@
       <c r="T17" s="1">
         <v>0</v>
       </c>
-      <c r="U17" s="5">
-        <v>12</v>
+      <c r="U17" s="1">
+        <v>0</v>
       </c>
       <c r="V17" s="5">
         <v>12</v>
       </c>
-      <c r="W17" s="1">
-        <v>80000</v>
+      <c r="W17" s="5">
+        <v>12</v>
       </c>
       <c r="X17" s="1">
         <v>80000</v>
       </c>
       <c r="Y17" s="1">
+        <v>80000</v>
+      </c>
+      <c r="Z17" s="1">
         <v>18000</v>
       </c>
-      <c r="Z17" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="2" t="s">
-        <v>55</v>
+      <c r="AA17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:28">
-      <c r="Q18" s="1"/>
-      <c r="S18" s="1"/>
+    <row r="18" customHeight="1" spans="3:29">
+      <c r="R18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="5"/>
+      <c r="U18" s="1"/>
       <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
     </row>
-    <row r="19" customHeight="1" spans="3:28">
+    <row r="19" customHeight="1" spans="3:29">
       <c r="C19" s="1">
         <v>13</v>
       </c>
@@ -2750,19 +2775,19 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K19" s="1">
         <v>400</v>
@@ -2776,48 +2801,49 @@
       <c r="N19" s="1">
         <v>300</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O19" s="1"/>
+      <c r="P19" s="1">
         <v>78</v>
       </c>
-      <c r="P19" s="1">
+      <c r="Q19" s="1">
         <v>80</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="R19" s="1">
         <v>13</v>
       </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
       <c r="S19" s="1">
         <v>0</v>
       </c>
       <c r="T19" s="1">
         <v>0</v>
       </c>
-      <c r="U19" s="5">
-        <v>13</v>
+      <c r="U19" s="1">
+        <v>0</v>
       </c>
       <c r="V19" s="5">
         <v>13</v>
       </c>
-      <c r="W19" s="1">
-        <v>90000</v>
+      <c r="W19" s="5">
+        <v>13</v>
       </c>
       <c r="X19" s="1">
         <v>90000</v>
       </c>
       <c r="Y19" s="1">
+        <v>90000</v>
+      </c>
+      <c r="Z19" s="1">
         <v>18000</v>
       </c>
-      <c r="Z19" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="2" t="s">
-        <v>55</v>
+      <c r="AA19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:28">
+    <row r="20" customHeight="1" spans="3:29">
       <c r="C20" s="1">
         <v>14</v>
       </c>
@@ -2828,19 +2854,19 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G20" s="1">
         <v>2</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" ref="K20:K30" si="6">K19+150</f>
@@ -2858,50 +2884,51 @@
         <f t="shared" ref="N20:N30" si="9">N19+100</f>
         <v>400</v>
       </c>
-      <c r="O20" s="1">
-        <f t="shared" ref="O20:O30" si="10">O19+6</f>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1">
+        <f t="shared" ref="P20:P30" si="10">P19+6</f>
         <v>84</v>
       </c>
-      <c r="P20" s="1">
-        <f t="shared" ref="P20:P30" si="11">P19+6</f>
+      <c r="Q20" s="1">
+        <f t="shared" ref="Q20:Q30" si="11">Q19+6</f>
         <v>86</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="R20" s="1">
         <v>14</v>
       </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
       <c r="S20" s="1">
         <v>0</v>
       </c>
       <c r="T20" s="1">
         <v>0</v>
       </c>
-      <c r="U20" s="5">
-        <v>14</v>
+      <c r="U20" s="1">
+        <v>0</v>
       </c>
       <c r="V20" s="5">
         <v>14</v>
       </c>
-      <c r="W20" s="1">
-        <v>100000</v>
+      <c r="W20" s="5">
+        <v>14</v>
       </c>
       <c r="X20" s="1">
         <v>100000</v>
       </c>
       <c r="Y20" s="1">
+        <v>100000</v>
+      </c>
+      <c r="Z20" s="1">
         <v>18000</v>
       </c>
-      <c r="Z20" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="2" t="s">
-        <v>55</v>
+      <c r="AA20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:28">
+    <row r="21" customHeight="1" spans="3:29">
       <c r="C21" s="1">
         <v>15</v>
       </c>
@@ -2912,19 +2939,19 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G21" s="1">
         <v>3</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" si="6"/>
@@ -2942,50 +2969,51 @@
         <f t="shared" si="9"/>
         <v>500</v>
       </c>
-      <c r="O21" s="1">
+      <c r="O21" s="1"/>
+      <c r="P21" s="1">
         <f t="shared" si="10"/>
         <v>90</v>
       </c>
-      <c r="P21" s="1">
+      <c r="Q21" s="1">
         <f t="shared" si="11"/>
         <v>92</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="R21" s="1">
         <v>15</v>
       </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
       <c r="S21" s="1">
         <v>0</v>
       </c>
       <c r="T21" s="1">
         <v>0</v>
       </c>
-      <c r="U21" s="5">
-        <v>15</v>
+      <c r="U21" s="1">
+        <v>0</v>
       </c>
       <c r="V21" s="5">
         <v>15</v>
       </c>
-      <c r="W21" s="1">
-        <v>120000</v>
+      <c r="W21" s="5">
+        <v>15</v>
       </c>
       <c r="X21" s="1">
         <v>120000</v>
       </c>
       <c r="Y21" s="1">
+        <v>120000</v>
+      </c>
+      <c r="Z21" s="1">
         <v>18000</v>
       </c>
-      <c r="Z21" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="2" t="s">
-        <v>55</v>
+      <c r="AA21" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:28">
+    <row r="22" customHeight="1" spans="3:29">
       <c r="C22" s="1">
         <v>16</v>
       </c>
@@ -2996,19 +3024,19 @@
         <v>2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G22" s="1">
         <v>4</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" si="6"/>
@@ -3027,49 +3055,52 @@
         <v>600</v>
       </c>
       <c r="O22" s="1">
+        <v>40</v>
+      </c>
+      <c r="P22" s="1">
         <f t="shared" si="10"/>
         <v>96</v>
       </c>
-      <c r="P22" s="1">
+      <c r="Q22" s="1">
         <f t="shared" si="11"/>
         <v>98</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="R22" s="1">
         <v>16</v>
       </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
       <c r="S22" s="1">
         <v>0</v>
       </c>
       <c r="T22" s="1">
         <v>0</v>
       </c>
-      <c r="U22" s="5">
-        <v>16</v>
+      <c r="U22" s="1">
+        <v>0</v>
       </c>
       <c r="V22" s="5">
         <v>16</v>
       </c>
-      <c r="W22" s="1">
-        <v>140000</v>
+      <c r="W22" s="5">
+        <v>16</v>
       </c>
       <c r="X22" s="1">
         <v>140000</v>
       </c>
       <c r="Y22" s="1">
+        <v>140000</v>
+      </c>
+      <c r="Z22" s="1">
         <v>18000</v>
       </c>
-      <c r="Z22" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="2" t="s">
-        <v>55</v>
+      <c r="AA22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:28">
+    <row r="23" customHeight="1" spans="3:29">
       <c r="C23" s="1">
         <v>17</v>
       </c>
@@ -3080,19 +3111,19 @@
         <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" s="1">
         <v>5</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" si="6"/>
@@ -3110,50 +3141,54 @@
         <f t="shared" si="9"/>
         <v>700</v>
       </c>
-      <c r="O23" s="1">
+      <c r="O23" s="2">
+        <f t="shared" ref="O23:O30" si="12">O22+30</f>
+        <v>70</v>
+      </c>
+      <c r="P23" s="1">
         <f t="shared" si="10"/>
         <v>102</v>
       </c>
-      <c r="P23" s="1">
+      <c r="Q23" s="1">
         <f t="shared" si="11"/>
         <v>104</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="R23" s="1">
         <v>17</v>
       </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
       <c r="S23" s="1">
         <v>0</v>
       </c>
       <c r="T23" s="1">
         <v>0</v>
       </c>
-      <c r="U23" s="5">
-        <v>17</v>
+      <c r="U23" s="1">
+        <v>0</v>
       </c>
       <c r="V23" s="5">
         <v>17</v>
       </c>
-      <c r="W23" s="1">
-        <v>160000</v>
+      <c r="W23" s="5">
+        <v>17</v>
       </c>
       <c r="X23" s="1">
         <v>160000</v>
       </c>
       <c r="Y23" s="1">
+        <v>160000</v>
+      </c>
+      <c r="Z23" s="1">
         <v>18000</v>
       </c>
-      <c r="Z23" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="2" t="s">
-        <v>55</v>
+      <c r="AA23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:28">
+    <row r="24" customHeight="1" spans="3:29">
       <c r="C24" s="1">
         <v>18</v>
       </c>
@@ -3164,19 +3199,19 @@
         <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24" s="1">
         <v>6</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="6"/>
@@ -3194,50 +3229,54 @@
         <f t="shared" si="9"/>
         <v>800</v>
       </c>
-      <c r="O24" s="1">
+      <c r="O24" s="2">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+      <c r="P24" s="1">
         <f t="shared" si="10"/>
         <v>108</v>
       </c>
-      <c r="P24" s="1">
+      <c r="Q24" s="1">
         <f t="shared" si="11"/>
         <v>110</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="R24" s="1">
         <v>18</v>
       </c>
-      <c r="R24" s="1">
-        <v>0</v>
-      </c>
       <c r="S24" s="1">
         <v>0</v>
       </c>
       <c r="T24" s="1">
         <v>0</v>
       </c>
-      <c r="U24" s="5">
-        <v>18</v>
+      <c r="U24" s="1">
+        <v>0</v>
       </c>
       <c r="V24" s="5">
         <v>18</v>
       </c>
-      <c r="W24" s="1">
-        <v>180000</v>
+      <c r="W24" s="5">
+        <v>18</v>
       </c>
       <c r="X24" s="1">
         <v>180000</v>
       </c>
       <c r="Y24" s="1">
+        <v>180000</v>
+      </c>
+      <c r="Z24" s="1">
         <v>18000</v>
       </c>
-      <c r="Z24" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="2" t="s">
-        <v>55</v>
+      <c r="AA24" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:28">
+    <row r="25" customHeight="1" spans="3:29">
       <c r="C25" s="1">
         <v>19</v>
       </c>
@@ -3248,19 +3287,19 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G25" s="1">
         <v>7</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" si="6"/>
@@ -3278,50 +3317,54 @@
         <f t="shared" si="9"/>
         <v>900</v>
       </c>
-      <c r="O25" s="1">
+      <c r="O25" s="2">
+        <f t="shared" si="12"/>
+        <v>130</v>
+      </c>
+      <c r="P25" s="1">
         <f t="shared" si="10"/>
         <v>114</v>
       </c>
-      <c r="P25" s="1">
+      <c r="Q25" s="1">
         <f t="shared" si="11"/>
         <v>116</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="R25" s="1">
         <v>19</v>
       </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
       <c r="S25" s="1">
         <v>0</v>
       </c>
       <c r="T25" s="1">
         <v>0</v>
       </c>
-      <c r="U25" s="5">
-        <v>19</v>
+      <c r="U25" s="1">
+        <v>0</v>
       </c>
       <c r="V25" s="5">
         <v>19</v>
       </c>
-      <c r="W25" s="1">
-        <v>200000</v>
+      <c r="W25" s="5">
+        <v>19</v>
       </c>
       <c r="X25" s="1">
         <v>200000</v>
       </c>
       <c r="Y25" s="1">
+        <v>200000</v>
+      </c>
+      <c r="Z25" s="1">
         <v>18000</v>
       </c>
-      <c r="Z25" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="2" t="s">
-        <v>55</v>
+      <c r="AA25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:28">
+    <row r="26" customHeight="1" spans="3:29">
       <c r="C26" s="1">
         <v>20</v>
       </c>
@@ -3332,19 +3375,19 @@
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G26" s="1">
         <v>8</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="6"/>
@@ -3362,50 +3405,54 @@
         <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-      <c r="O26" s="1">
+      <c r="O26" s="2">
+        <f t="shared" si="12"/>
+        <v>160</v>
+      </c>
+      <c r="P26" s="1">
         <f t="shared" si="10"/>
         <v>120</v>
       </c>
-      <c r="P26" s="1">
+      <c r="Q26" s="1">
         <f t="shared" si="11"/>
         <v>122</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="R26" s="1">
         <v>20</v>
       </c>
-      <c r="R26" s="1">
-        <v>0</v>
-      </c>
       <c r="S26" s="1">
         <v>0</v>
       </c>
       <c r="T26" s="1">
         <v>0</v>
       </c>
-      <c r="U26" s="5">
-        <v>20</v>
+      <c r="U26" s="1">
+        <v>0</v>
       </c>
       <c r="V26" s="5">
         <v>20</v>
       </c>
-      <c r="W26" s="1">
-        <v>220000</v>
+      <c r="W26" s="5">
+        <v>20</v>
       </c>
       <c r="X26" s="1">
         <v>220000</v>
       </c>
       <c r="Y26" s="1">
+        <v>220000</v>
+      </c>
+      <c r="Z26" s="1">
         <v>18000</v>
       </c>
-      <c r="Z26" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="2" t="s">
-        <v>55</v>
+      <c r="AA26" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="3:28">
+    <row r="27" customHeight="1" spans="3:29">
       <c r="C27" s="1">
         <v>21</v>
       </c>
@@ -3416,19 +3463,19 @@
         <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="1">
         <v>9</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="6"/>
@@ -3446,50 +3493,54 @@
         <f t="shared" si="9"/>
         <v>1100</v>
       </c>
-      <c r="O27" s="1">
+      <c r="O27" s="2">
+        <f t="shared" si="12"/>
+        <v>190</v>
+      </c>
+      <c r="P27" s="1">
         <f t="shared" si="10"/>
         <v>126</v>
       </c>
-      <c r="P27" s="1">
+      <c r="Q27" s="1">
         <f t="shared" si="11"/>
         <v>128</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="R27" s="1">
         <v>21</v>
       </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
       <c r="S27" s="1">
         <v>0</v>
       </c>
       <c r="T27" s="1">
         <v>0</v>
       </c>
-      <c r="U27" s="5">
-        <v>21</v>
+      <c r="U27" s="1">
+        <v>0</v>
       </c>
       <c r="V27" s="5">
         <v>21</v>
       </c>
-      <c r="W27" s="1">
-        <v>240000</v>
+      <c r="W27" s="5">
+        <v>21</v>
       </c>
       <c r="X27" s="1">
         <v>240000</v>
       </c>
       <c r="Y27" s="1">
+        <v>240000</v>
+      </c>
+      <c r="Z27" s="1">
         <v>18000</v>
       </c>
-      <c r="Z27" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="2" t="s">
-        <v>55</v>
+      <c r="AA27" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:28">
+    <row r="28" customHeight="1" spans="3:29">
       <c r="C28" s="1">
         <v>22</v>
       </c>
@@ -3500,19 +3551,19 @@
         <v>2</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G28" s="1">
         <v>10</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="6"/>
@@ -3530,50 +3581,54 @@
         <f t="shared" si="9"/>
         <v>1200</v>
       </c>
-      <c r="O28" s="1">
+      <c r="O28" s="2">
+        <f t="shared" si="12"/>
+        <v>220</v>
+      </c>
+      <c r="P28" s="1">
         <f t="shared" si="10"/>
         <v>132</v>
       </c>
-      <c r="P28" s="1">
+      <c r="Q28" s="1">
         <f t="shared" si="11"/>
         <v>134</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="R28" s="1">
         <v>22</v>
       </c>
-      <c r="R28" s="1">
-        <v>0</v>
-      </c>
       <c r="S28" s="1">
         <v>0</v>
       </c>
       <c r="T28" s="1">
         <v>0</v>
       </c>
-      <c r="U28" s="5">
-        <v>22</v>
+      <c r="U28" s="1">
+        <v>0</v>
       </c>
       <c r="V28" s="5">
         <v>22</v>
       </c>
-      <c r="W28" s="1">
-        <v>260000</v>
+      <c r="W28" s="5">
+        <v>22</v>
       </c>
       <c r="X28" s="1">
         <v>260000</v>
       </c>
       <c r="Y28" s="1">
+        <v>260000</v>
+      </c>
+      <c r="Z28" s="1">
         <v>18000</v>
       </c>
-      <c r="Z28" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="2" t="s">
-        <v>55</v>
+      <c r="AA28" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:28">
+    <row r="29" customHeight="1" spans="3:29">
       <c r="C29" s="1">
         <v>23</v>
       </c>
@@ -3584,19 +3639,19 @@
         <v>2</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G29" s="1">
         <v>11</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" si="6"/>
@@ -3614,50 +3669,54 @@
         <f t="shared" si="9"/>
         <v>1300</v>
       </c>
-      <c r="O29" s="1">
+      <c r="O29" s="2">
+        <f t="shared" si="12"/>
+        <v>250</v>
+      </c>
+      <c r="P29" s="1">
         <f t="shared" si="10"/>
         <v>138</v>
       </c>
-      <c r="P29" s="1">
+      <c r="Q29" s="1">
         <f t="shared" si="11"/>
         <v>140</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="R29" s="1">
         <v>23</v>
       </c>
-      <c r="R29" s="1">
-        <v>0</v>
-      </c>
       <c r="S29" s="1">
         <v>0</v>
       </c>
       <c r="T29" s="1">
         <v>0</v>
       </c>
-      <c r="U29" s="5">
-        <v>23</v>
+      <c r="U29" s="1">
+        <v>0</v>
       </c>
       <c r="V29" s="5">
         <v>23</v>
       </c>
-      <c r="W29" s="1">
-        <v>280000</v>
+      <c r="W29" s="5">
+        <v>23</v>
       </c>
       <c r="X29" s="1">
         <v>280000</v>
       </c>
       <c r="Y29" s="1">
+        <v>280000</v>
+      </c>
+      <c r="Z29" s="1">
         <v>18000</v>
       </c>
-      <c r="Z29" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="2" t="s">
-        <v>55</v>
+      <c r="AA29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:28">
+    <row r="30" customHeight="1" spans="3:29">
       <c r="C30" s="1">
         <v>24</v>
       </c>
@@ -3668,19 +3727,19 @@
         <v>2</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G30" s="1">
         <v>12</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="6"/>
@@ -3698,52 +3757,56 @@
         <f t="shared" si="9"/>
         <v>1400</v>
       </c>
-      <c r="O30" s="1">
+      <c r="O30" s="2">
+        <f t="shared" si="12"/>
+        <v>280</v>
+      </c>
+      <c r="P30" s="1">
         <f t="shared" si="10"/>
         <v>144</v>
       </c>
-      <c r="P30" s="1">
+      <c r="Q30" s="1">
         <f t="shared" si="11"/>
         <v>146</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="R30" s="1">
         <v>24</v>
       </c>
-      <c r="R30" s="1">
-        <v>0</v>
-      </c>
       <c r="S30" s="1">
         <v>0</v>
       </c>
       <c r="T30" s="1">
         <v>0</v>
       </c>
-      <c r="U30" s="5">
-        <v>24</v>
+      <c r="U30" s="1">
+        <v>0</v>
       </c>
       <c r="V30" s="5">
         <v>24</v>
       </c>
-      <c r="W30" s="1">
-        <v>300000</v>
+      <c r="W30" s="5">
+        <v>24</v>
       </c>
       <c r="X30" s="1">
         <v>300000</v>
       </c>
       <c r="Y30" s="1">
+        <v>300000</v>
+      </c>
+      <c r="Z30" s="1">
         <v>18000</v>
       </c>
-      <c r="Z30" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="2" t="s">
-        <v>55</v>
+      <c r="AA30" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5 J3:V5 Z3:AA5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3 O4 O5 C3:N5 P3:W5 AA3:AB5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
